--- a/CORTES DE CAJA/2026/5)MAYO/LISTA DE LAS VENTAS SEMANA 17 DE MAYO 26 06.xlsx
+++ b/CORTES DE CAJA/2026/5)MAYO/LISTA DE LAS VENTAS SEMANA 17 DE MAYO 26 06.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3DFB3D-75DB-4FDF-8D31-2196D9E5D094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD69C601-3D49-4A9E-9DC0-3CD7F7CFF4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1191,27 +1191,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1251,8 +1230,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1262,6 +1259,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1850,23 +1850,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -1879,14 +1879,14 @@
         <f>SUM(Tabla1[Importa])</f>
         <v>1771</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -1917,19 +1917,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>25</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -1951,21 +1951,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C36" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -1987,19 +1987,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>64</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -2018,19 +2018,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>120</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -2052,19 +2052,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>22.5</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -2086,19 +2086,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>9</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -2120,19 +2120,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -2154,19 +2154,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -2188,19 +2188,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -2219,19 +2219,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -2250,19 +2250,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>170</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -2281,17 +2281,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>266</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -2310,17 +2310,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -2342,17 +2342,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>18</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -2374,17 +2374,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -2403,17 +2403,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>53</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -2432,17 +2432,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -2461,17 +2461,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -2490,17 +2490,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -2526,7 +2526,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -2545,19 +2545,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>185</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -2576,17 +2576,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>35</v>
       </c>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -2605,23 +2605,23 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G26))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M26" s="38" t="s">
+      <c r="M26" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="38"/>
+      <c r="N26" s="31"/>
       <c r="O26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="38" t="s">
+      <c r="P26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -2640,21 +2640,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G27))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="27"/>
-      <c r="O27" s="30">
+      <c r="N27" s="20"/>
+      <c r="O27" s="23">
         <v>2673</v>
       </c>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="34"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="27"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -2673,17 +2673,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G28))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>25</v>
       </c>
-      <c r="M28" s="28"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="37"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="30"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29">
         <f t="shared" si="0"/>
@@ -2702,12 +2702,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G29))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="34"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="27"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -2722,12 +2722,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G30))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M30" s="28"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="37"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="30"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -2742,12 +2742,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G31))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M31" s="26"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="34"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="27"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -2762,12 +2762,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G32))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M32" s="28"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="37"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="30"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -2782,12 +2782,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G33))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="34"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="27"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -2802,12 +2802,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G34))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M34" s="28"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="37"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="30"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -2822,12 +2822,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G35))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M35" s="26"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="34"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="27"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -2842,12 +2842,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G36))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M36" s="28"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="37"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="30"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -2862,12 +2862,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G37))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M37" s="26"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="32"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="34"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="27"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -2882,12 +2882,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G38))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M38" s="28"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="36"/>
-      <c r="R38" s="37"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="30"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -2902,12 +2902,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G39))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M39" s="26"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="34"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="27"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -2922,12 +2922,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G40))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M40" s="28"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="37"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="30"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -2942,12 +2942,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G41))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M41" s="26"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="34"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="27"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -2962,12 +2962,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G42))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M42" s="28"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="35"/>
-      <c r="Q42" s="36"/>
-      <c r="R42" s="37"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="30"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -2982,12 +2982,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G43))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="34"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="25"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="27"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -3002,12 +3002,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G44))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M44" s="28"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="37"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="30"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -3022,12 +3022,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G45))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M45" s="26"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="34"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="27"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="str">
@@ -3042,12 +3042,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G46))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M46" s="28"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="37"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="30"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="str">
@@ -3062,12 +3062,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G47))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M47" s="26"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="34"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="25"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="27"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="str">
@@ -3082,12 +3082,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G48))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M48" s="28"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="35"/>
-      <c r="Q48" s="36"/>
-      <c r="R48" s="37"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="30"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="str">
@@ -3102,12 +3102,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G49))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M49" s="26"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="34"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="23"/>
+      <c r="P49" s="25"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="27"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="18" t="str">
@@ -3122,12 +3122,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G50))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M50" s="28"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="36"/>
-      <c r="R50" s="37"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="30"/>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="18" t="str">
@@ -3142,12 +3142,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G51))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M51" s="26"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="34"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="23"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="26"/>
+      <c r="R51" s="27"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="18" t="str">
@@ -3162,12 +3162,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G52))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M52" s="28"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="36"/>
-      <c r="R52" s="37"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="30"/>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="18" t="str">
@@ -3886,33 +3886,19 @@
   </sheetData>
   <autoFilter ref="B4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="48">
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:R50"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="P51:R52"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="P45:R46"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:R48"/>
-    <mergeCell ref="P31:R32"/>
-    <mergeCell ref="P33:R34"/>
-    <mergeCell ref="P35:R36"/>
-    <mergeCell ref="P37:R38"/>
-    <mergeCell ref="P39:R40"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="M31:N32"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="M35:N36"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="M39:N40"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P41:R42"/>
+    <mergeCell ref="P43:R44"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="M27:N28"/>
@@ -3921,19 +3907,33 @@
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="P27:R28"/>
     <mergeCell ref="P29:R30"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P41:R42"/>
-    <mergeCell ref="P43:R44"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="M39:N40"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="P31:R32"/>
+    <mergeCell ref="P33:R34"/>
+    <mergeCell ref="P35:R36"/>
+    <mergeCell ref="P37:R38"/>
+    <mergeCell ref="P39:R40"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:R48"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:R50"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="P51:R52"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -3972,23 +3972,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -4001,14 +4001,14 @@
         <f>SUM(Tabla110[Importa])</f>
         <v>1565</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -4039,17 +4039,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>12</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla110[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -4071,21 +4071,21 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>630</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -4104,19 +4104,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>120</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -4138,19 +4138,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>360</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -4172,19 +4172,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>86.5</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -4206,19 +4206,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>108</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -4237,19 +4237,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>8</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -4268,19 +4268,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -4299,19 +4299,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -4330,19 +4330,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -4361,19 +4361,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -4392,17 +4392,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>60</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -4424,17 +4424,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50.5</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -4444,17 +4444,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -4464,17 +4464,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -4484,17 +4484,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -4504,17 +4504,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -4524,17 +4524,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -4544,17 +4544,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -4568,7 +4568,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -4578,19 +4578,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -4600,17 +4600,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -4626,17 +4626,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -4648,15 +4648,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -4668,15 +4668,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -4688,10 +4688,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -4708,10 +4708,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -4728,10 +4728,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -4748,10 +4748,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -4768,10 +4768,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -4788,10 +4788,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -4808,10 +4808,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -4828,10 +4828,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -4848,10 +4848,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -4868,10 +4868,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -4888,10 +4888,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -4928,10 +4928,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -4948,10 +4948,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -4968,10 +4968,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -4988,10 +4988,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -5821,32 +5821,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -5885,23 +5885,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -5914,14 +5914,14 @@
         <f>SUM(Tabla111[Importa])</f>
         <v>2215</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -5952,19 +5952,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>18</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla111[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -5986,21 +5986,21 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>580.5</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6">
         <f>IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -6022,19 +6022,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85.5</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7">
         <f>IF(ISNUMBER(E7), IF(ISNUMBER(C6), C6+1, 1), "")</f>
@@ -6056,19 +6056,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C68" si="0">IF(ISNUMBER(E8), IF(ISNUMBER(C7), C7+1, 1), "")</f>
@@ -6090,19 +6090,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>48</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -6121,19 +6121,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>166</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -6152,19 +6152,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>70</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -6183,19 +6183,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -6214,19 +6214,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -6245,19 +6245,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -6276,19 +6276,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>115</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -6307,17 +6307,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -6336,17 +6336,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -6365,17 +6365,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>38</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -6394,17 +6394,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>180</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -6423,17 +6423,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>120</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -6452,17 +6452,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -6481,17 +6481,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>82</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -6513,17 +6513,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>450</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -6537,7 +6537,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -6547,19 +6547,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -6569,17 +6569,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -6595,17 +6595,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -6621,15 +6621,15 @@
       <c r="N27" s="15">
         <v>1910</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -6645,15 +6645,15 @@
       <c r="N28" s="15">
         <v>4501</v>
       </c>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -6665,10 +6665,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -6685,10 +6685,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -6705,10 +6705,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -6725,10 +6725,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -6745,10 +6745,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -6765,10 +6765,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -6785,10 +6785,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -6805,10 +6805,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -6825,10 +6825,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -6845,10 +6845,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -6865,10 +6865,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -6885,10 +6885,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -6905,10 +6905,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -6925,10 +6925,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -6945,10 +6945,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -6965,10 +6965,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -7798,32 +7798,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="9" priority="1">
@@ -7862,23 +7862,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -7891,14 +7891,14 @@
         <f>SUM(Tabla112[Importa])</f>
         <v>2279</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -7929,19 +7929,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>19</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla112[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -7963,21 +7963,21 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>486</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -7999,19 +7999,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>356.5</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -8030,19 +8030,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -8061,19 +8061,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -8095,19 +8095,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>117</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -8129,19 +8129,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>270</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -8163,19 +8163,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>64</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -8197,19 +8197,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -8231,19 +8231,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -8265,19 +8265,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>31.5</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -8296,17 +8296,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>120</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -8328,17 +8328,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85.5</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -8360,17 +8360,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -8392,17 +8392,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>262</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -8421,17 +8421,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>75</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -8450,17 +8450,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -8479,17 +8479,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>110</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -8511,17 +8511,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>83</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -8547,7 +8547,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -8557,19 +8557,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -8579,17 +8579,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -8605,17 +8605,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -8631,15 +8631,15 @@
       <c r="N27" s="15">
         <v>2426</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -8655,15 +8655,15 @@
       <c r="N28" s="15">
         <v>2272</v>
       </c>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -8675,10 +8675,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -8695,10 +8695,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -8715,10 +8715,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -8735,10 +8735,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -8755,10 +8755,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -8775,10 +8775,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -8795,10 +8795,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -8815,10 +8815,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -8835,10 +8835,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -8855,10 +8855,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -8875,10 +8875,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -8895,10 +8895,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -8915,10 +8915,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -8935,10 +8935,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -8955,10 +8955,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -8975,10 +8975,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -9808,32 +9808,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="7" priority="1">
@@ -9872,23 +9872,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -9901,14 +9901,14 @@
         <f>SUM(Tabla113[Importa])</f>
         <v>5028</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -9939,19 +9939,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>24</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla113[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -9973,21 +9973,21 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>472.5</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -10009,19 +10009,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>266</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -10043,19 +10043,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>900</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -10077,19 +10077,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>67.5</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -10111,19 +10111,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -10145,19 +10145,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -10179,19 +10179,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -10210,19 +10210,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -10241,19 +10241,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>24</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -10272,19 +10272,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>3</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -10303,17 +10303,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>500</v>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -10335,17 +10335,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>450</v>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -10367,17 +10367,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>405</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -10399,17 +10399,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>62.5</v>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -10428,17 +10428,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>700</v>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -10457,17 +10457,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>55</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -10489,17 +10489,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>180</v>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
@@ -10518,17 +10518,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>220</v>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
@@ -10551,7 +10551,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
@@ -10570,19 +10570,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>55</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
@@ -10601,17 +10601,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>142</v>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
@@ -10636,17 +10636,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
@@ -10671,17 +10671,17 @@
       <c r="N27" s="15">
         <v>2673</v>
       </c>
-      <c r="O27" s="40" t="s">
+      <c r="O27" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
@@ -10709,17 +10709,17 @@
       <c r="N28" s="15">
         <v>1910</v>
       </c>
-      <c r="O28" s="40" t="s">
+      <c r="O28" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -10735,12 +10735,12 @@
       <c r="N29" s="15">
         <v>4501</v>
       </c>
-      <c r="O29" s="40" t="s">
+      <c r="O29" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -10761,12 +10761,12 @@
       <c r="N30" s="15">
         <v>2426</v>
       </c>
-      <c r="O30" s="40" t="s">
+      <c r="O30" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -10787,12 +10787,12 @@
       <c r="N31" s="15">
         <v>2272</v>
       </c>
-      <c r="O31" s="40" t="s">
+      <c r="O31" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -10813,12 +10813,12 @@
       <c r="N32" s="15">
         <v>1500</v>
       </c>
-      <c r="O32" s="40" t="s">
+      <c r="O32" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -10839,12 +10839,12 @@
       <c r="N33" s="15">
         <v>15282</v>
       </c>
-      <c r="O33" s="40" t="s">
+      <c r="O33" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -10861,10 +10861,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -10881,10 +10881,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -10901,10 +10901,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -10921,10 +10921,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -10941,10 +10941,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -10961,10 +10961,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -10981,10 +10981,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -11001,10 +11001,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -11021,10 +11021,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -11041,10 +11041,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -11061,10 +11061,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -11894,32 +11894,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11958,23 +11958,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -11987,14 +11987,14 @@
         <f>SUM(Tabla114[Importa])</f>
         <v>1103</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -12025,19 +12025,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>10</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla114[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -12056,21 +12056,21 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -12089,19 +12089,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>120</v>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -12120,19 +12120,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -12154,19 +12154,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -12185,19 +12185,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>70</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -12219,19 +12219,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>436</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -12253,19 +12253,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>61.5</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -12287,19 +12287,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>262</v>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -12321,19 +12321,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -12352,19 +12352,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>85</v>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -12374,17 +12374,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -12394,17 +12394,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -12414,17 +12414,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -12434,17 +12434,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -12454,17 +12454,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -12474,17 +12474,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -12494,17 +12494,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -12514,17 +12514,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -12538,7 +12538,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -12548,19 +12548,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -12570,17 +12570,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -12596,17 +12596,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -12622,15 +12622,15 @@
       <c r="N27" s="15">
         <v>5230</v>
       </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -12642,15 +12642,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -12662,10 +12662,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -12682,10 +12682,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -12702,10 +12702,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -12722,10 +12722,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -12742,10 +12742,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -12762,10 +12762,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -12782,10 +12782,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -12802,10 +12802,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -12822,10 +12822,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -12842,10 +12842,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -12862,10 +12862,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -12882,10 +12882,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -12902,10 +12902,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -12922,10 +12922,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -12942,10 +12942,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -12962,10 +12962,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -13795,32 +13795,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -13858,23 +13858,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -13887,14 +13887,14 @@
         <f>SUM(Tabla115[Importa])</f>
         <v>0</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -13925,12 +13925,12 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -13945,21 +13945,21 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="K5" s="38"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -13969,19 +13969,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -13991,19 +13991,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -14013,19 +14013,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -14035,19 +14035,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -14057,19 +14057,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -14079,19 +14079,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -14101,19 +14101,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -14123,19 +14123,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -14145,19 +14145,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -14167,17 +14167,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -14187,17 +14187,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -14207,17 +14207,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -14227,17 +14227,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -14247,17 +14247,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -14267,17 +14267,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -14287,17 +14287,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -14307,17 +14307,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -14331,7 +14331,7 @@
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -14341,19 +14341,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -14363,17 +14363,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -14389,17 +14389,17 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="38" t="s">
+      <c r="O26" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="38"/>
-      <c r="R26" s="38"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -14411,15 +14411,15 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="42"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="41"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -14431,15 +14431,15 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="41"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46151.801464004631</v>
+        <v>46153.723043865743</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -14451,10 +14451,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="41"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -14471,10 +14471,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -14491,10 +14491,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -14511,10 +14511,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="40"/>
+      <c r="Q32" s="40"/>
+      <c r="R32" s="41"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -14531,10 +14531,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="41"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -14551,10 +14551,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="41"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -14571,10 +14571,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="41"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -14591,10 +14591,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="40"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -14611,10 +14611,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="42"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="40"/>
+      <c r="R37" s="41"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -14631,10 +14631,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -14651,10 +14651,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="42"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -14671,10 +14671,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="42"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -14691,10 +14691,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="41"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -14711,10 +14711,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -14731,10 +14731,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="40"/>
+      <c r="R43" s="41"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -14751,10 +14751,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="40"/>
+      <c r="R44" s="41"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -15584,32 +15584,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="1" priority="1">
